--- a/templates/office/EMP_TST_040_성능시험결과보고서.xlsx
+++ b/templates/office/EMP_TST_040_성능시험결과보고서.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>

--- a/templates/office/EMP_TST_040_성능시험결과보고서.xlsx
+++ b/templates/office/EMP_TST_040_성능시험결과보고서.xlsx
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 부하(Stress) 테스트, 동시 접속 TPS 및 AI 추론 응답 시간 검증 결과서</t>
+          <t>SyncFlow AI 시스템 부하(Stress) 테스트, 동시 접속 TPS 및 AI 추론 응답 시간 검증 결과서</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>심의 목록 다차원 검색 및 페이징</t>
+          <t>검증 목록 다차원 검색 및 페이징</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>단일 시안 이미지 OCR 비전 추출</t>
+          <t>단일 계약·도서 이미지 OCR 비전 추출</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -856,7 +856,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>100대 금지어 룰셋 인덱스 스크리닝</t>
+          <t>100대 독소조항 룰셋 인덱스 스크리닝</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>LLM 대체 문구 자동 추천 추론</t>
+          <t>LLM 대체 조항 자동 추천 추론</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>복합 다중 슬라이드(10P) 전체 심의 파이프라인</t>
+          <t>복합 다중 슬라이드(10P) 전체 검증 파이프라인</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>심의 의견서 PDF 렌더링 다운로드</t>
+          <t>검증 의견서 PDF 렌더링 다운로드</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ProductLab 전성분·실증 마스터 배치 동기화</t>
+          <t>PLM-Nexus 자재BOM·시험검증 마스터 배치 동기화</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>MarketingHub 회신 웹훅 동시 발송</t>
+          <t>SRM-Portal 회신 웹훅 동시 발송</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
